--- a/healthcare_forms/014_ppe_request_form--healthcare_forms.xlsx
+++ b/healthcare_forms/014_ppe_request_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>description_text</t>
+          <t>description_text_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>description_html</t>
+          <t>description_html_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Description Html</t>
+          <t>Description Html 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>output_file_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Output File 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Description 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -917,7 +917,7 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1010,7 +1010,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1027,7 +1027,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
